--- a/templates/THAIPUT_REGISTRATION_v6.1.xlsx
+++ b/templates/THAIPUT_REGISTRATION_v6.1.xlsx
@@ -17,10 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY HH:MM"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -59,11 +56,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +431,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,11 @@
       <c r="C2" s="2" t="n">
         <v>1560000</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MẪU — sửa theo bảng giá thật</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,18 +523,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -580,343 +584,12 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46218.41666666666</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>hoa@example.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Lê Thị Hoa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Gói 12 buổi</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="G2">
-        <f>VLOOKUP(D2,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H2" s="2">
-        <f>VLOOKUP(D2,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46219.41666666666</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dung@example.com</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn Dũng</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Gói 24 buổi</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="G3">
-        <f>VLOOKUP(D3,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H3" s="2">
-        <f>VLOOKUP(D3,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46220.41666666666</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>minhanh@example.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Trần Minh Anh</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Gói 12 buổi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="G4">
-        <f>VLOOKUP(D4,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H4" s="2">
-        <f>VLOOKUP(D4,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46221.41666666666</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>bao@example.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Phạm Quốc Bảo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Gói 48 buổi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>S004</t>
-        </is>
-      </c>
-      <c r="G5">
-        <f>VLOOKUP(D5,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H5" s="2">
-        <f>VLOOKUP(D5,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46222.41666666666</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>linh@example.com</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Võ Thuỳ Linh</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gói 12 buổi</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="G6">
-        <f>VLOOKUP(D6,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H6" s="2">
-        <f>VLOOKUP(D6,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46223.41666666666</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nam@example.com</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Đặng Hoàng Nam</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Gói 24 buổi</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Chưa thanh toán</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>S006</t>
-        </is>
-      </c>
-      <c r="G7">
-        <f>VLOOKUP(D7,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H7" s="2">
-        <f>VLOOKUP(D7,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46224.41666666666</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>tam@example.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bùi Thanh Tâm</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Gói 12 buổi</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Đã thanh toán</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>S007</t>
-        </is>
-      </c>
-      <c r="G8">
-        <f>VLOOKUP(D8,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H8" s="2">
-        <f>VLOOKUP(D8,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46225.41666666666</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ngan@example.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Lý Kim Ngân</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Gói 48 buổi</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Chưa thanh toán</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>S008</t>
-        </is>
-      </c>
-      <c r="G9">
-        <f>VLOOKUP(D9,PACKAGES!A:B,2,FALSE)</f>
-        <v/>
-      </c>
-      <c r="H9" s="2">
-        <f>VLOOKUP(D9,PACKAGES!A:C,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="I9" t="inlineStr"/>
-    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Chưa thanh toán,Đã thanh toán"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>